--- a/clientportal/Contracts and Amendments - 5777_GR-CR.xlsx
+++ b/clientportal/Contracts and Amendments - 5777_GR-CR.xlsx
@@ -435,468 +435,468 @@
     <t>Contrato por una suma global</t>
   </si>
   <si>
+    <t>Finalizado</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00063</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00063-C01</t>
+  </si>
+  <si>
+    <t>Contratación de una Arquitecta por demanda 1 para apoyo a los proyectos de infraestructura del Programa</t>
+  </si>
+  <si>
+    <t>Brindar servicios profesionales por demanda en el área de la Arquitectura con el fin de apoyar los procesos de diseño, construcción, equipamiento, supervisión e inspección de las obras de infraestructura del Programa.</t>
+  </si>
+  <si>
+    <t>Andrea Vargas Fernández</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00066</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00066-C01</t>
+  </si>
+  <si>
+    <t>Contratación de una Gestora Metodológica para el desarrollo de la Estrategia de Centros Cívicos sin Paredes en comunidades de la Zona Huetar Norte 2</t>
+  </si>
+  <si>
+    <t>Gestor metodológico Zona Huetar 2</t>
+  </si>
+  <si>
+    <t>Melissa María Rodríguez Ríos</t>
+  </si>
+  <si>
+    <t>Contrato basado en el pago de honorarios fijos o de una comisión de éxito</t>
+  </si>
+  <si>
+    <t>Ejecución con Enmiendas</t>
+  </si>
+  <si>
+    <t>Unidad Coordinadora del Programa de Seguridad Ciudadana y  prevención de la Violencia (UCP), Préstamo N° 4871/OC-CR, Banco Interamericano de Desarrollo</t>
+  </si>
+  <si>
+    <t>SAN JOSÉ</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00074</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00074-C01</t>
+  </si>
+  <si>
+    <t>Contratación de Facilitador (a) 8 Zona Huetar Norte</t>
+  </si>
+  <si>
+    <t>Facilitador 8 Zona Huetar Norte</t>
+  </si>
+  <si>
+    <t>Marylize Benavides Murillo</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00080</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00080-C01</t>
+  </si>
+  <si>
+    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 1</t>
+  </si>
+  <si>
+    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 1</t>
+  </si>
+  <si>
+    <t>Estíbaliz Ríos Madriz</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00081</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00081-C01</t>
+  </si>
+  <si>
+    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 2</t>
+  </si>
+  <si>
+    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 2</t>
+  </si>
+  <si>
+    <t>Raquel Ureña Haug</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00082</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00082-C01</t>
+  </si>
+  <si>
+    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 3</t>
+  </si>
+  <si>
+    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 3</t>
+  </si>
+  <si>
+    <t>Daniel Mora Montoya</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00083</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00083-C01</t>
+  </si>
+  <si>
+    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 4</t>
+  </si>
+  <si>
+    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 4</t>
+  </si>
+  <si>
+    <t>Kerlyn Alejandra Luna Ramírez</t>
+  </si>
+  <si>
+    <t>Suma Alzada</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00084</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00084-C01</t>
+  </si>
+  <si>
+    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 5</t>
+  </si>
+  <si>
+    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 5</t>
+  </si>
+  <si>
+    <t>Bladimir Garita Salgado</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00085</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00085-C01</t>
+  </si>
+  <si>
+    <t>Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 6</t>
+  </si>
+  <si>
+    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 6</t>
+  </si>
+  <si>
+    <t>María José Álvarez Blanco</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00086</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00086-C01</t>
+  </si>
+  <si>
+    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 7</t>
+  </si>
+  <si>
+    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 7</t>
+  </si>
+  <si>
+    <t>Filys Dante Parra Gómez</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00087</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00087-C01</t>
+  </si>
+  <si>
+    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 8</t>
+  </si>
+  <si>
+    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 8</t>
+  </si>
+  <si>
+    <t>Rolando Castillo Rojas</t>
+  </si>
+  <si>
+    <t>Rescindido</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00088</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00088-C01</t>
+  </si>
+  <si>
+    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 9</t>
+  </si>
+  <si>
+    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 9</t>
+  </si>
+  <si>
+    <t>Juan Pablo Obando Ramos</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00089</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00089-C01</t>
+  </si>
+  <si>
+    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 10</t>
+  </si>
+  <si>
+    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 10</t>
+  </si>
+  <si>
+    <t>Juan de Dios Quirós Rodríguez</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00090</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00090-C01</t>
+  </si>
+  <si>
+    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 11</t>
+  </si>
+  <si>
+    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 11</t>
+  </si>
+  <si>
+    <t>Liliana Castro Araya</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00091</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00091-C01</t>
+  </si>
+  <si>
+    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 12</t>
+  </si>
+  <si>
+    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 12</t>
+  </si>
+  <si>
+    <t>Laura García Gorgona</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00096</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00096-C01</t>
+  </si>
+  <si>
+    <t>Contratación de un Ingeniero Eléctrico por demanda I para apoyo a los proyectos de infraestructura del PSCIGMV</t>
+  </si>
+  <si>
+    <t>Ingeniero Eléctrico 1 por demanda obras de infraestructura PSCIGMV</t>
+  </si>
+  <si>
+    <t>Yong Xiang Zheng Arrieta</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00114</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00114-C01</t>
+  </si>
+  <si>
+    <t>Contratación de persona profesional en Derecho 8 para apoyo al Fondo de Regularización de Personas Migrantes</t>
+  </si>
+  <si>
+    <t>Consultoría apoyo regularización migratoria Derecho 8</t>
+  </si>
+  <si>
+    <t>Silvia Margoth Corrales Vargas</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00123</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00123-C01</t>
+  </si>
+  <si>
+    <t>Contratación de persona profesional en Derecho 17 para apoyo al Fondo de Regularización de Personas Migrantes</t>
+  </si>
+  <si>
+    <t>Apoyar a la UCP y la GTIGMV en la ejecución de entrevistas de elegibilidad y resolución de solicitudes de refugio y regularización migratoria en diferentes categorías de extranjería o actividades similares de otros mecanismos regularización migratoria en general, para contribuir al cumplimiento de las actividades de la estrategia de apoyo al Fondo de Regularización de Personas Migrantes, del Componente 2 “Fortalecimiento de las capacidades institucionales para atender los flujos migratorios”.</t>
+  </si>
+  <si>
+    <t>Melanie Natalia Arguedas Ramos</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00131</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00131-C01</t>
+  </si>
+  <si>
+    <t>Profesional en Derecho 25 apoyo al Fondo de Regularización de Personas Migrantes, en el marco del Programa Seguridad Ciudadana y Prevención de la Violencia Inclusión de Grupos Migrantes Vulnerables</t>
+  </si>
+  <si>
+    <t>Gloria Helena Chaves Blanco</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00132</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00132-C01</t>
+  </si>
+  <si>
+    <t>Contratación de Profesional en Derecho 26 para apoyo al Fondo de Regularización de Personas Migrantes</t>
+  </si>
+  <si>
+    <t>Miriam Ivonne Reyes González</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00133</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00133-C01</t>
+  </si>
+  <si>
+    <t>Contratación de persona profesional en Derecho 27 para apoyo al Fondo de Regularización de Personas Migrantes</t>
+  </si>
+  <si>
+    <t>Consultoría apoyo regularización migratoria Derecho 27</t>
+  </si>
+  <si>
+    <t>Madelein Granados Quesada</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00134</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00134-C01</t>
+  </si>
+  <si>
+    <t>Profesional en Derecho 28 para apoyo al Fondo de Regularización de Personas Migrantes</t>
+  </si>
+  <si>
+    <t>María Felicia Jiménez Blanco</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00135</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00135-C01</t>
+  </si>
+  <si>
+    <t>Contratación de persona profesional en Derecho 29 para apoyo al Fondo de Regularización de Personas Migrantes, en el marco del PSCIGMV.</t>
+  </si>
+  <si>
+    <t>Consultoría apoyo regularización migratoria Derecho 29</t>
+  </si>
+  <si>
+    <t>Alanna Dennise Rodríguez Gómez</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00136</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00136-C01</t>
+  </si>
+  <si>
+    <t>Contratación de persona profesional en Derecho 30 para apoyo al Fondo de Regularización de Personas Migrantes</t>
+  </si>
+  <si>
+    <t>Consultoría apoyo regularización migratoria Derecho 30</t>
+  </si>
+  <si>
+    <t>Yocelyn Ivannia Matarrita</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00137</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00137-C01</t>
+  </si>
+  <si>
+    <t>Profesional en Derecho 31 para apoyo al Fondo de Regularización de Personas Migrantes</t>
+  </si>
+  <si>
+    <t>Dayana Pérez Núñez</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00138</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00138-C01</t>
+  </si>
+  <si>
+    <t>Contratación de persona profesional en Derecho 32 para apoyo al Fondo de Regularización de Personas Migrantes</t>
+  </si>
+  <si>
+    <t>Consultoría apoyo regularización migratoria Derecho 32</t>
+  </si>
+  <si>
+    <t>William Danilo Ramírez Buitrago</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00139</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00139-C01</t>
+  </si>
+  <si>
+    <t>Contratación de persona profesional en Derecho 33 para apoyo al Fondo de Regularización de Personas Migrantes</t>
+  </si>
+  <si>
+    <t>Consultoría apoyo regularización migratoria Derecho 33</t>
+  </si>
+  <si>
+    <t>Maria Jose Rivera Castillo</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00140</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00140-C01</t>
+  </si>
+  <si>
+    <t>Contratación de persona profesional en Derecho 34 para apoyo al Fondo de Regularización de Personas Migrantes</t>
+  </si>
+  <si>
+    <t>Consultoría apoyo regularización migratoria Derecho 34</t>
+  </si>
+  <si>
+    <t>Laura Rojas Jimenez</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00141</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00141-C01</t>
+  </si>
+  <si>
+    <t>Contratación de persona profesional en Derecho 35 para apoyo al Fondo de Regularización de Personas Migrantes</t>
+  </si>
+  <si>
+    <t>Consultoría apoyo regularización migratoria Derecho 35</t>
+  </si>
+  <si>
+    <t>Yohana Vargas Jimenez</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00142</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00142-C01</t>
+  </si>
+  <si>
+    <t>Contratación de persona profesional en Derecho 36 para apoyo al Fondo de Regularización de Personas Migrantes</t>
+  </si>
+  <si>
+    <t>Consultoría apoyo regularización migratoria Derecho 36</t>
+  </si>
+  <si>
+    <t>Fauricio Gerardo Vega Morales</t>
+  </si>
+  <si>
     <t>Expirado</t>
   </si>
   <si>
-    <t>CR-J0002-P00063</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00063-C01</t>
-  </si>
-  <si>
-    <t>Contratación de una Arquitecta por demanda 1 para apoyo a los proyectos de infraestructura del Programa</t>
-  </si>
-  <si>
-    <t>Brindar servicios profesionales por demanda en el área de la Arquitectura con el fin de apoyar los procesos de diseño, construcción, equipamiento, supervisión e inspección de las obras de infraestructura del Programa.</t>
-  </si>
-  <si>
-    <t>Andrea Vargas Fernández</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00066</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00066-C01</t>
-  </si>
-  <si>
-    <t>Contratación de una Gestora Metodológica para el desarrollo de la Estrategia de Centros Cívicos sin Paredes en comunidades de la Zona Huetar Norte 2</t>
-  </si>
-  <si>
-    <t>Gestor metodológico Zona Huetar 2</t>
-  </si>
-  <si>
-    <t>Melissa María Rodríguez Ríos</t>
-  </si>
-  <si>
-    <t>Contrato basado en el pago de honorarios fijos o de una comisión de éxito</t>
-  </si>
-  <si>
-    <t>Ejecución con Enmiendas</t>
-  </si>
-  <si>
-    <t>Unidad Coordinadora del Programa de Seguridad Ciudadana y  prevención de la Violencia (UCP), Préstamo N° 4871/OC-CR, Banco Interamericano de Desarrollo</t>
-  </si>
-  <si>
-    <t>SAN JOSÉ</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00074</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00074-C01</t>
-  </si>
-  <si>
-    <t>Contratación de Facilitador (a) 8 Zona Huetar Norte</t>
-  </si>
-  <si>
-    <t>Facilitador 8 Zona Huetar Norte</t>
-  </si>
-  <si>
-    <t>Marylize Benavides Murillo</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00080</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00080-C01</t>
-  </si>
-  <si>
-    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 1</t>
-  </si>
-  <si>
-    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 1</t>
-  </si>
-  <si>
-    <t>Estíbaliz Ríos Madriz</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00081</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00081-C01</t>
-  </si>
-  <si>
-    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 2</t>
-  </si>
-  <si>
-    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 2</t>
-  </si>
-  <si>
-    <t>Raquel Ureña Haug</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00082</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00082-C01</t>
-  </si>
-  <si>
-    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 3</t>
-  </si>
-  <si>
-    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 3</t>
-  </si>
-  <si>
-    <t>Daniel Mora Montoya</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00083</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00083-C01</t>
-  </si>
-  <si>
-    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 4</t>
-  </si>
-  <si>
-    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 4</t>
-  </si>
-  <si>
-    <t>Kerlyn Alejandra Luna Ramírez</t>
-  </si>
-  <si>
-    <t>Suma Alzada</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00084</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00084-C01</t>
-  </si>
-  <si>
-    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 5</t>
-  </si>
-  <si>
-    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 5</t>
-  </si>
-  <si>
-    <t>Bladimir Garita Salgado</t>
-  </si>
-  <si>
-    <t>Finalizado</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00085</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00085-C01</t>
-  </si>
-  <si>
-    <t>Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 6</t>
-  </si>
-  <si>
-    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 6</t>
-  </si>
-  <si>
-    <t>María José Álvarez Blanco</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00086</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00086-C01</t>
-  </si>
-  <si>
-    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 7</t>
-  </si>
-  <si>
-    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 7</t>
-  </si>
-  <si>
-    <t>Filys Dante Parra Gómez</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00087</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00087-C01</t>
-  </si>
-  <si>
-    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 8</t>
-  </si>
-  <si>
-    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 8</t>
-  </si>
-  <si>
-    <t>Rolando Castillo Rojas</t>
-  </si>
-  <si>
-    <t>Rescindido</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00088</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00088-C01</t>
-  </si>
-  <si>
-    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 9</t>
-  </si>
-  <si>
-    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 9</t>
-  </si>
-  <si>
-    <t>Juan Pablo Obando Ramos</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00089</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00089-C01</t>
-  </si>
-  <si>
-    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 10</t>
-  </si>
-  <si>
-    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 10</t>
-  </si>
-  <si>
-    <t>Juan de Dios Quirós Rodríguez</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00090</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00090-C01</t>
-  </si>
-  <si>
-    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 11</t>
-  </si>
-  <si>
-    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 11</t>
-  </si>
-  <si>
-    <t>Liliana Castro Araya</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00091</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00091-C01</t>
-  </si>
-  <si>
-    <t>Contratación de Facilitador(a) fortalecimiento Centros Cívicos sin Paredes 12</t>
-  </si>
-  <si>
-    <t>Facilitador fortalecimiento Centros Cívicos sin Paredes 12</t>
-  </si>
-  <si>
-    <t>Laura García Gorgona</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00096</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00096-C01</t>
-  </si>
-  <si>
-    <t>Contratación de un Ingeniero Eléctrico por demanda I para apoyo a los proyectos de infraestructura del PSCIGMV</t>
-  </si>
-  <si>
-    <t>Ingeniero Eléctrico 1 por demanda obras de infraestructura PSCIGMV</t>
-  </si>
-  <si>
-    <t>Yong Xiang Zheng Arrieta</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00114</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00114-C01</t>
-  </si>
-  <si>
-    <t>Contratación de persona profesional en Derecho 8 para apoyo al Fondo de Regularización de Personas Migrantes</t>
-  </si>
-  <si>
-    <t>Consultoría apoyo regularización migratoria Derecho 8</t>
-  </si>
-  <si>
-    <t>Silvia Margoth Corrales Vargas</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00123</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00123-C01</t>
-  </si>
-  <si>
-    <t>Contratación de persona profesional en Derecho 17 para apoyo al Fondo de Regularización de Personas Migrantes</t>
-  </si>
-  <si>
-    <t>Apoyar a la UCP y la GTIGMV en la ejecución de entrevistas de elegibilidad y resolución de solicitudes de refugio y regularización migratoria en diferentes categorías de extranjería o actividades similares de otros mecanismos regularización migratoria en general, para contribuir al cumplimiento de las actividades de la estrategia de apoyo al Fondo de Regularización de Personas Migrantes, del Componente 2 “Fortalecimiento de las capacidades institucionales para atender los flujos migratorios”.</t>
-  </si>
-  <si>
-    <t>Melanie Natalia Arguedas Ramos</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00131</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00131-C01</t>
-  </si>
-  <si>
-    <t>Profesional en Derecho 25 apoyo al Fondo de Regularización de Personas Migrantes, en el marco del Programa Seguridad Ciudadana y Prevención de la Violencia Inclusión de Grupos Migrantes Vulnerables</t>
-  </si>
-  <si>
-    <t>Gloria Helena Chaves Blanco</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00132</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00132-C01</t>
-  </si>
-  <si>
-    <t>Contratación de Profesional en Derecho 26 para apoyo al Fondo de Regularización de Personas Migrantes</t>
-  </si>
-  <si>
-    <t>Miriam Ivonne Reyes González</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00133</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00133-C01</t>
-  </si>
-  <si>
-    <t>Contratación de persona profesional en Derecho 27 para apoyo al Fondo de Regularización de Personas Migrantes</t>
-  </si>
-  <si>
-    <t>Consultoría apoyo regularización migratoria Derecho 27</t>
-  </si>
-  <si>
-    <t>Madelein Granados Quesada</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00134</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00134-C01</t>
-  </si>
-  <si>
-    <t>Profesional en Derecho 28 para apoyo al Fondo de Regularización de Personas Migrantes</t>
-  </si>
-  <si>
-    <t>María Felicia Jiménez Blanco</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00135</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00135-C01</t>
-  </si>
-  <si>
-    <t>Contratación de persona profesional en Derecho 29 para apoyo al Fondo de Regularización de Personas Migrantes, en el marco del PSCIGMV.</t>
-  </si>
-  <si>
-    <t>Consultoría apoyo regularización migratoria Derecho 29</t>
-  </si>
-  <si>
-    <t>Alanna Dennise Rodríguez Gómez</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00136</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00136-C01</t>
-  </si>
-  <si>
-    <t>Contratación de persona profesional en Derecho 30 para apoyo al Fondo de Regularización de Personas Migrantes</t>
-  </si>
-  <si>
-    <t>Consultoría apoyo regularización migratoria Derecho 30</t>
-  </si>
-  <si>
-    <t>Yocelyn Ivannia Matarrita</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00137</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00137-C01</t>
-  </si>
-  <si>
-    <t>Profesional en Derecho 31 para apoyo al Fondo de Regularización de Personas Migrantes</t>
-  </si>
-  <si>
-    <t>Dayana Pérez Núñez</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00138</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00138-C01</t>
-  </si>
-  <si>
-    <t>Contratación de persona profesional en Derecho 32 para apoyo al Fondo de Regularización de Personas Migrantes</t>
-  </si>
-  <si>
-    <t>Consultoría apoyo regularización migratoria Derecho 32</t>
-  </si>
-  <si>
-    <t>William Danilo Ramírez Buitrago</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00139</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00139-C01</t>
-  </si>
-  <si>
-    <t>Contratación de persona profesional en Derecho 33 para apoyo al Fondo de Regularización de Personas Migrantes</t>
-  </si>
-  <si>
-    <t>Consultoría apoyo regularización migratoria Derecho 33</t>
-  </si>
-  <si>
-    <t>Maria Jose Rivera Castillo</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00140</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00140-C01</t>
-  </si>
-  <si>
-    <t>Contratación de persona profesional en Derecho 34 para apoyo al Fondo de Regularización de Personas Migrantes</t>
-  </si>
-  <si>
-    <t>Consultoría apoyo regularización migratoria Derecho 34</t>
-  </si>
-  <si>
-    <t>Laura Rojas Jimenez</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00141</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00141-C01</t>
-  </si>
-  <si>
-    <t>Contratación de persona profesional en Derecho 35 para apoyo al Fondo de Regularización de Personas Migrantes</t>
-  </si>
-  <si>
-    <t>Consultoría apoyo regularización migratoria Derecho 35</t>
-  </si>
-  <si>
-    <t>Yohana Vargas Jimenez</t>
-  </si>
-  <si>
-    <t>CR-J0002-P00142</t>
-  </si>
-  <si>
-    <t>5777GRCR-CR-J0002-P00142-C01</t>
-  </si>
-  <si>
-    <t>Contratación de persona profesional en Derecho 36 para apoyo al Fondo de Regularización de Personas Migrantes</t>
-  </si>
-  <si>
-    <t>Consultoría apoyo regularización migratoria Derecho 36</t>
-  </si>
-  <si>
-    <t>Fauricio Gerardo Vega Morales</t>
-  </si>
-  <si>
     <t>CR-J0002-P00143</t>
   </si>
   <si>
@@ -1284,18 +1284,18 @@
     <t>Suma alzada - Diseño y construcción</t>
   </si>
   <si>
+    <t>Arbitraje</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
+    <t>San José </t>
+  </si>
+  <si>
     <t>CRC</t>
   </si>
   <si>
-    <t>Arbitraje</t>
-  </si>
-  <si>
-    <t>Sí</t>
-  </si>
-  <si>
-    <t>San José </t>
-  </si>
-  <si>
     <t>CR-J0002-P00197</t>
   </si>
   <si>
@@ -1413,6 +1413,21 @@
     <t>Wilbert Jafet Varela Jimenez</t>
   </si>
   <si>
+    <t>CR-J0002-P00214</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00214-C01</t>
+  </si>
+  <si>
+    <t>Contratación de servicios profesionales por demanda como conciliador(a) técnico(a) para asesoramiento en el proyecto, Diseño, construcción y equipamiento de la Unidad de Refugio y obras conexas, 1.305</t>
+  </si>
+  <si>
+    <t>Contratación de servicios profesionales por demanda como Conciliador(a) Técnico(a) para asesoramiento en el diseño, construcción y equipamiento de la Unidad de Refugio y obras conexas</t>
+  </si>
+  <si>
+    <t>Álvaro Lara Vargas</t>
+  </si>
+  <si>
     <t>CR-J0002-P00215</t>
   </si>
   <si>
@@ -1711,6 +1726,21 @@
   </si>
   <si>
     <t>Yoen Arguedas López:</t>
+  </si>
+  <si>
+    <t>CR-J0002-P00249</t>
+  </si>
+  <si>
+    <t>5777GRCR-CR-J0002-P00249-C01</t>
+  </si>
+  <si>
+    <t>Contratación de apoyo técnico-administrativo 26 para trámites del Fondo de Regularización de Personas Migrantes</t>
+  </si>
+  <si>
+    <t>Consultoría apoyo a trámites de regularización migratoria 26</t>
+  </si>
+  <si>
+    <t>Ermes Antonio Campos Monge</t>
   </si>
   <si>
     <t>CR-J0002-P00250</t>
@@ -2190,7 +2220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI89"/>
+  <dimension ref="A1:AI91"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18.6640625" style="1" customWidth="1"/>
@@ -3120,7 +3150,7 @@
       </c>
       <c r="I11" s="2"/>
       <c r="J11" t="s" s="1">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="K11" t="n" s="6">
         <v>46101</v>
@@ -3180,19 +3210,19 @@
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" t="s" s="1">
+        <v>182</v>
+      </c>
+      <c r="B12" t="s" s="1">
         <v>183</v>
       </c>
-      <c r="B12" t="s" s="1">
+      <c r="C12" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="C12" t="s" s="2">
+      <c r="D12" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="D12" t="s" s="2">
+      <c r="E12" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>121</v>
@@ -3265,19 +3295,19 @@
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" t="s" s="1">
+        <v>187</v>
+      </c>
+      <c r="B13" t="s" s="1">
         <v>188</v>
       </c>
-      <c r="B13" t="s" s="1">
+      <c r="C13" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="C13" t="s" s="2">
+      <c r="D13" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="D13" t="s" s="2">
+      <c r="E13" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>121</v>
@@ -3290,7 +3320,7 @@
       </c>
       <c r="I13" s="2"/>
       <c r="J13" t="s" s="1">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="K13" t="n" s="6">
         <v>46162</v>
@@ -3350,19 +3380,19 @@
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" t="s" s="1">
+        <v>192</v>
+      </c>
+      <c r="B14" t="s" s="1">
         <v>193</v>
       </c>
-      <c r="B14" t="s" s="1">
+      <c r="C14" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="C14" t="s" s="2">
+      <c r="D14" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="D14" t="s" s="2">
+      <c r="E14" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>121</v>
@@ -3375,7 +3405,7 @@
       </c>
       <c r="I14" s="2"/>
       <c r="J14" t="s" s="1">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K14" t="n" s="6">
         <v>46160</v>
@@ -3435,19 +3465,19 @@
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" t="s" s="1">
+        <v>198</v>
+      </c>
+      <c r="B15" t="s" s="1">
         <v>199</v>
       </c>
-      <c r="B15" t="s" s="1">
+      <c r="C15" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="C15" t="s" s="2">
+      <c r="D15" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="D15" t="s" s="2">
+      <c r="E15" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="E15" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>121</v>
@@ -3460,7 +3490,7 @@
       </c>
       <c r="I15" s="2"/>
       <c r="J15" t="s" s="1">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="K15" t="n" s="6">
         <v>46160</v>
@@ -3520,19 +3550,19 @@
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" t="s" s="1">
+        <v>203</v>
+      </c>
+      <c r="B16" t="s" s="1">
         <v>204</v>
       </c>
-      <c r="B16" t="s" s="1">
+      <c r="C16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="C16" t="s" s="2">
+      <c r="D16" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="D16" t="s" s="2">
+      <c r="E16" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="E16" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>121</v>
@@ -3605,19 +3635,19 @@
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" t="s" s="1">
+        <v>208</v>
+      </c>
+      <c r="B17" t="s" s="1">
         <v>209</v>
       </c>
-      <c r="B17" t="s" s="1">
+      <c r="C17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="C17" t="s" s="2">
+      <c r="D17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="D17" t="s" s="2">
+      <c r="E17" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="E17" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>121</v>
@@ -3630,7 +3660,7 @@
       </c>
       <c r="I17" s="2"/>
       <c r="J17" t="s" s="1">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="K17" t="n" s="6">
         <v>46163</v>
@@ -3690,19 +3720,19 @@
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" t="s" s="1">
+        <v>213</v>
+      </c>
+      <c r="B18" t="s" s="1">
         <v>214</v>
       </c>
-      <c r="B18" t="s" s="1">
+      <c r="C18" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="C18" t="s" s="2">
+      <c r="D18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="D18" t="s" s="2">
+      <c r="E18" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="E18" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>121</v>
@@ -3775,19 +3805,19 @@
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" t="s" s="1">
+        <v>218</v>
+      </c>
+      <c r="B19" t="s" s="1">
         <v>219</v>
       </c>
-      <c r="B19" t="s" s="1">
+      <c r="C19" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="C19" t="s" s="2">
+      <c r="D19" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="D19" t="s" s="2">
+      <c r="E19" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="E19" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>121</v>
@@ -3860,19 +3890,19 @@
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" t="s" s="1">
+        <v>223</v>
+      </c>
+      <c r="B20" t="s" s="1">
         <v>224</v>
       </c>
-      <c r="B20" t="s" s="1">
+      <c r="C20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="C20" t="s" s="2">
+      <c r="D20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="D20" t="s" s="2">
+      <c r="E20" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>121</v>
@@ -3945,19 +3975,19 @@
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" t="s" s="1">
+        <v>228</v>
+      </c>
+      <c r="B21" t="s" s="1">
         <v>229</v>
       </c>
-      <c r="B21" t="s" s="1">
+      <c r="C21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="C21" t="s" s="2">
+      <c r="D21" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="D21" t="s" s="2">
+      <c r="E21" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="E21" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>121</v>
@@ -4028,19 +4058,19 @@
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" t="s" s="1">
+        <v>233</v>
+      </c>
+      <c r="B22" t="s" s="1">
         <v>234</v>
       </c>
-      <c r="B22" t="s" s="1">
+      <c r="C22" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="C22" t="s" s="2">
+      <c r="D22" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="E22" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="E22" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>121</v>
@@ -4111,19 +4141,19 @@
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" t="s" s="1">
+        <v>237</v>
+      </c>
+      <c r="B23" t="s" s="1">
         <v>238</v>
       </c>
-      <c r="B23" t="s" s="1">
+      <c r="C23" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="C23" t="s" s="2">
+      <c r="D23" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="E23" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="D23" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="E23" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>121</v>
@@ -4194,19 +4224,19 @@
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" t="s" s="1">
+        <v>241</v>
+      </c>
+      <c r="B24" t="s" s="1">
         <v>242</v>
       </c>
-      <c r="B24" t="s" s="1">
+      <c r="C24" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="C24" t="s" s="2">
+      <c r="D24" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="D24" t="s" s="2">
+      <c r="E24" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="E24" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>121</v>
@@ -4279,19 +4309,19 @@
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" t="s" s="1">
+        <v>246</v>
+      </c>
+      <c r="B25" t="s" s="1">
         <v>247</v>
       </c>
-      <c r="B25" t="s" s="1">
+      <c r="C25" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="C25" t="s" s="2">
+      <c r="D25" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="E25" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="D25" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="E25" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>121</v>
@@ -4362,19 +4392,19 @@
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A26" t="s" s="1">
+        <v>250</v>
+      </c>
+      <c r="B26" t="s" s="1">
         <v>251</v>
       </c>
-      <c r="B26" t="s" s="1">
+      <c r="C26" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="C26" t="s" s="2">
+      <c r="D26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="D26" t="s" s="2">
+      <c r="E26" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="E26" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>121</v>
@@ -4387,7 +4417,7 @@
       </c>
       <c r="I26" s="2"/>
       <c r="J26" t="s" s="1">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K26" t="n" s="6">
         <v>46099</v>
@@ -4447,19 +4477,19 @@
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" t="s" s="1">
+        <v>255</v>
+      </c>
+      <c r="B27" t="s" s="1">
         <v>256</v>
       </c>
-      <c r="B27" t="s" s="1">
+      <c r="C27" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="C27" t="s" s="2">
+      <c r="D27" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="D27" t="s" s="2">
+      <c r="E27" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="E27" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>121</v>
@@ -4532,19 +4562,19 @@
     </row>
     <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" t="s" s="1">
+        <v>260</v>
+      </c>
+      <c r="B28" t="s" s="1">
         <v>261</v>
       </c>
-      <c r="B28" t="s" s="1">
+      <c r="C28" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="C28" t="s" s="2">
+      <c r="D28" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="E28" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="D28" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="E28" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>121</v>
@@ -4615,19 +4645,19 @@
     </row>
     <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" t="s" s="1">
+        <v>264</v>
+      </c>
+      <c r="B29" t="s" s="1">
         <v>265</v>
       </c>
-      <c r="B29" t="s" s="1">
+      <c r="C29" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="C29" t="s" s="2">
+      <c r="D29" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="D29" t="s" s="2">
+      <c r="E29" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="E29" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>121</v>
@@ -4700,19 +4730,19 @@
     </row>
     <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" t="s" s="1">
+        <v>269</v>
+      </c>
+      <c r="B30" t="s" s="1">
         <v>270</v>
       </c>
-      <c r="B30" t="s" s="1">
+      <c r="C30" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="C30" t="s" s="2">
+      <c r="D30" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="D30" t="s" s="2">
+      <c r="E30" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="E30" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>121</v>
@@ -4785,19 +4815,19 @@
     </row>
     <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" t="s" s="1">
+        <v>274</v>
+      </c>
+      <c r="B31" t="s" s="1">
         <v>275</v>
       </c>
-      <c r="B31" t="s" s="1">
+      <c r="C31" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="C31" t="s" s="2">
+      <c r="D31" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="D31" t="s" s="2">
+      <c r="E31" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="E31" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>121</v>
@@ -4810,7 +4840,7 @@
       </c>
       <c r="I31" s="2"/>
       <c r="J31" t="s" s="1">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="K31" t="n" s="6">
         <v>46098</v>
@@ -4870,19 +4900,19 @@
     </row>
     <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A32" t="s" s="1">
+        <v>279</v>
+      </c>
+      <c r="B32" t="s" s="1">
         <v>280</v>
       </c>
-      <c r="B32" t="s" s="1">
+      <c r="C32" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="C32" t="s" s="2">
+      <c r="D32" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="D32" t="s" s="2">
+      <c r="E32" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="E32" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>121</v>
@@ -4955,19 +4985,19 @@
     </row>
     <row r="33" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A33" t="s" s="1">
+        <v>284</v>
+      </c>
+      <c r="B33" t="s" s="1">
         <v>285</v>
       </c>
-      <c r="B33" t="s" s="1">
+      <c r="C33" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="C33" t="s" s="2">
+      <c r="D33" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="D33" t="s" s="2">
+      <c r="E33" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>121</v>
@@ -4980,7 +5010,7 @@
       </c>
       <c r="I33" s="2"/>
       <c r="J33" t="s" s="1">
-        <v>136</v>
+        <v>289</v>
       </c>
       <c r="K33" t="n" s="6">
         <v>46097</v>
@@ -5745,7 +5775,7 @@
       </c>
       <c r="I42" s="2"/>
       <c r="J42" t="s" s="1">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K42" t="n" s="6">
         <v>46133</v>
@@ -6255,7 +6285,7 @@
       </c>
       <c r="I48" s="2"/>
       <c r="J48" t="s" s="1">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K48" t="n" s="6">
         <v>46139</v>
@@ -6425,7 +6455,7 @@
       </c>
       <c r="I50" s="2"/>
       <c r="J50" t="s" s="1">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="K50" t="n" s="6">
         <v>46136</v>
@@ -6510,7 +6540,7 @@
       </c>
       <c r="I51" s="2"/>
       <c r="J51" t="s" s="1">
-        <v>136</v>
+        <v>289</v>
       </c>
       <c r="K51" t="n" s="6">
         <v>46140</v>
@@ -6595,7 +6625,7 @@
       </c>
       <c r="I52" s="2"/>
       <c r="J52" t="s" s="1">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K52" t="n" s="6">
         <v>46136</v>
@@ -7117,10 +7147,10 @@
         <v>46602</v>
       </c>
       <c r="N58" t="s" s="1">
-        <v>419</v>
+        <v>125</v>
       </c>
       <c r="O58" t="n" s="3">
-        <v>1610690000</v>
+        <v>550500</v>
       </c>
       <c r="P58" t="n" s="3">
         <v>0</v>
@@ -7129,21 +7159,21 @@
         <v>0</v>
       </c>
       <c r="R58" t="n" s="3">
-        <v>1610690000</v>
+        <v>550500</v>
       </c>
       <c r="S58" s="2"/>
       <c r="T58" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="U58" s="2"/>
       <c r="V58" t="n" s="2">
         <v>9968</v>
       </c>
       <c r="W58" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="X58" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="Y58" t="s" s="2">
         <v>128</v>
@@ -7202,10 +7232,10 @@
         <v>46602</v>
       </c>
       <c r="N59" t="s" s="1">
-        <v>125</v>
+        <v>422</v>
       </c>
       <c r="O59" t="n" s="3">
-        <v>550500</v>
+        <v>1610690000</v>
       </c>
       <c r="P59" t="n" s="3">
         <v>0</v>
@@ -7214,21 +7244,21 @@
         <v>0</v>
       </c>
       <c r="R59" t="n" s="3">
-        <v>550500</v>
+        <v>1610690000</v>
       </c>
       <c r="S59" s="2"/>
       <c r="T59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="U59" s="2"/>
       <c r="V59" t="n" s="2">
         <v>9968</v>
       </c>
       <c r="W59" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="X59" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="Y59" t="s" s="2">
         <v>128</v>
@@ -7868,7 +7898,7 @@
       </c>
       <c r="I67" s="2"/>
       <c r="J67" t="s" s="1">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="K67" t="n" s="6">
         <v>46091</v>
@@ -7949,26 +7979,26 @@
         <v>122</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="I68" s="2"/>
       <c r="J68" t="s" s="1">
-        <v>182</v>
+        <v>124</v>
       </c>
       <c r="K68" t="n" s="6">
-        <v>46154</v>
+        <v>46117</v>
       </c>
       <c r="L68" t="n" s="6">
-        <v>46155</v>
+        <v>46290</v>
       </c>
       <c r="M68" t="n" s="6">
-        <v>46277</v>
+        <v>46592</v>
       </c>
       <c r="N68" t="s" s="1">
         <v>125</v>
       </c>
       <c r="O68" t="n" s="3">
-        <v>6400</v>
+        <v>15000</v>
       </c>
       <c r="P68" t="n" s="3">
         <v>0</v>
@@ -7977,7 +8007,7 @@
         <v>0</v>
       </c>
       <c r="R68" t="n" s="3">
-        <v>6400</v>
+        <v>15000</v>
       </c>
       <c r="S68" s="2"/>
       <c r="T68" t="s" s="2">
@@ -8038,16 +8068,16 @@
       </c>
       <c r="I69" s="2"/>
       <c r="J69" t="s" s="1">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="K69" t="n" s="6">
+        <v>46154</v>
+      </c>
+      <c r="L69" t="n" s="6">
         <v>46155</v>
       </c>
-      <c r="L69" t="n" s="6">
-        <v>46160</v>
-      </c>
       <c r="M69" t="n" s="6">
-        <v>46282</v>
+        <v>46277</v>
       </c>
       <c r="N69" t="s" s="1">
         <v>125</v>
@@ -8123,16 +8153,16 @@
       </c>
       <c r="I70" s="2"/>
       <c r="J70" t="s" s="1">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="K70" t="n" s="6">
-        <v>46205</v>
+        <v>46155</v>
       </c>
       <c r="L70" t="n" s="6">
-        <v>46206</v>
+        <v>46160</v>
       </c>
       <c r="M70" t="n" s="6">
-        <v>46328</v>
+        <v>46282</v>
       </c>
       <c r="N70" t="s" s="1">
         <v>125</v>
@@ -8208,16 +8238,16 @@
       </c>
       <c r="I71" s="2"/>
       <c r="J71" t="s" s="1">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="K71" t="n" s="6">
-        <v>46198</v>
+        <v>46205</v>
       </c>
       <c r="L71" t="n" s="6">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="M71" t="n" s="6">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="N71" t="s" s="1">
         <v>125</v>
@@ -8293,16 +8323,16 @@
       </c>
       <c r="I72" s="2"/>
       <c r="J72" t="s" s="1">
-        <v>198</v>
+        <v>148</v>
       </c>
       <c r="K72" t="n" s="6">
-        <v>46191</v>
+        <v>46198</v>
       </c>
       <c r="L72" t="n" s="6">
-        <v>46195</v>
+        <v>46205</v>
       </c>
       <c r="M72" t="n" s="6">
-        <v>46316</v>
+        <v>46327</v>
       </c>
       <c r="N72" t="s" s="1">
         <v>125</v>
@@ -8378,16 +8408,16 @@
       </c>
       <c r="I73" s="2"/>
       <c r="J73" t="s" s="1">
-        <v>124</v>
+        <v>197</v>
       </c>
       <c r="K73" t="n" s="6">
-        <v>46205</v>
+        <v>46191</v>
       </c>
       <c r="L73" t="n" s="6">
-        <v>46209</v>
+        <v>46195</v>
       </c>
       <c r="M73" t="n" s="6">
-        <v>46331</v>
+        <v>46316</v>
       </c>
       <c r="N73" t="s" s="1">
         <v>125</v>
@@ -8466,13 +8496,13 @@
         <v>124</v>
       </c>
       <c r="K74" t="n" s="6">
-        <v>46220</v>
+        <v>46205</v>
       </c>
       <c r="L74" t="n" s="6">
-        <v>46225</v>
+        <v>46209</v>
       </c>
       <c r="M74" t="n" s="6">
-        <v>46347</v>
+        <v>46331</v>
       </c>
       <c r="N74" t="s" s="1">
         <v>125</v>
@@ -8551,13 +8581,13 @@
         <v>124</v>
       </c>
       <c r="K75" t="n" s="6">
-        <v>46224</v>
+        <v>46220</v>
       </c>
       <c r="L75" t="n" s="6">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="M75" t="n" s="6">
-        <v>46352</v>
+        <v>46347</v>
       </c>
       <c r="N75" t="s" s="1">
         <v>125</v>
@@ -8636,13 +8666,13 @@
         <v>124</v>
       </c>
       <c r="K76" t="n" s="6">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="L76" t="n" s="6">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="M76" t="n" s="6">
-        <v>46347</v>
+        <v>46352</v>
       </c>
       <c r="N76" t="s" s="1">
         <v>125</v>
@@ -8721,13 +8751,13 @@
         <v>124</v>
       </c>
       <c r="K77" t="n" s="6">
-        <v>46226</v>
+        <v>46220</v>
       </c>
       <c r="L77" t="n" s="6">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="M77" t="n" s="6">
-        <v>46352</v>
+        <v>46347</v>
       </c>
       <c r="N77" t="s" s="1">
         <v>125</v>
@@ -8803,22 +8833,22 @@
       </c>
       <c r="I78" s="2"/>
       <c r="J78" t="s" s="1">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="K78" t="n" s="6">
-        <v>46191</v>
+        <v>46226</v>
       </c>
       <c r="L78" t="n" s="6">
-        <v>46204</v>
+        <v>46230</v>
       </c>
       <c r="M78" t="n" s="6">
-        <v>46326</v>
+        <v>46352</v>
       </c>
       <c r="N78" t="s" s="1">
         <v>125</v>
       </c>
       <c r="O78" t="n" s="3">
-        <v>9600</v>
+        <v>6400</v>
       </c>
       <c r="P78" t="n" s="3">
         <v>0</v>
@@ -8827,7 +8857,7 @@
         <v>0</v>
       </c>
       <c r="R78" t="n" s="3">
-        <v>9600</v>
+        <v>6400</v>
       </c>
       <c r="S78" s="2"/>
       <c r="T78" t="s" s="2">
@@ -8976,7 +9006,7 @@
         <v>148</v>
       </c>
       <c r="K80" t="n" s="6">
-        <v>46195</v>
+        <v>46191</v>
       </c>
       <c r="L80" t="n" s="6">
         <v>46204</v>
@@ -9011,10 +9041,10 @@
         <v>127</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="Z80" t="n" s="1">
         <v>10101</v>
@@ -9058,16 +9088,16 @@
       </c>
       <c r="I81" s="2"/>
       <c r="J81" t="s" s="1">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="K81" t="n" s="6">
-        <v>46197</v>
+        <v>46195</v>
       </c>
       <c r="L81" t="n" s="6">
-        <v>46219</v>
+        <v>46204</v>
       </c>
       <c r="M81" t="n" s="6">
-        <v>46341</v>
+        <v>46326</v>
       </c>
       <c r="N81" t="s" s="1">
         <v>125</v>
@@ -9143,16 +9173,16 @@
       </c>
       <c r="I82" s="2"/>
       <c r="J82" t="s" s="1">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="K82" t="n" s="6">
-        <v>46206</v>
+        <v>46197</v>
       </c>
       <c r="L82" t="n" s="6">
-        <v>46226</v>
+        <v>46219</v>
       </c>
       <c r="M82" t="n" s="6">
-        <v>46348</v>
+        <v>46341</v>
       </c>
       <c r="N82" t="s" s="1">
         <v>125</v>
@@ -9231,13 +9261,13 @@
         <v>124</v>
       </c>
       <c r="K83" t="n" s="6">
-        <v>46211</v>
+        <v>46206</v>
       </c>
       <c r="L83" t="n" s="6">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="M83" t="n" s="6">
-        <v>46352</v>
+        <v>46348</v>
       </c>
       <c r="N83" t="s" s="1">
         <v>125</v>
@@ -9266,10 +9296,10 @@
         <v>127</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="Z83" t="n" s="1">
         <v>10101</v>
@@ -9401,19 +9431,19 @@
         <v>124</v>
       </c>
       <c r="K85" t="n" s="6">
-        <v>46231</v>
+        <v>46211</v>
       </c>
       <c r="L85" t="n" s="6">
-        <v>46240</v>
+        <v>46230</v>
       </c>
       <c r="M85" t="n" s="6">
-        <v>46392</v>
+        <v>46352</v>
       </c>
       <c r="N85" t="s" s="1">
         <v>125</v>
       </c>
       <c r="O85" t="n" s="3">
-        <v>14000</v>
+        <v>9600</v>
       </c>
       <c r="P85" t="n" s="3">
         <v>0</v>
@@ -9422,7 +9452,7 @@
         <v>0</v>
       </c>
       <c r="R85" t="n" s="3">
-        <v>14000</v>
+        <v>9600</v>
       </c>
       <c r="S85" s="2"/>
       <c r="T85" t="s" s="2">
@@ -9489,10 +9519,10 @@
         <v>46231</v>
       </c>
       <c r="L86" t="n" s="6">
-        <v>46258</v>
+        <v>46240</v>
       </c>
       <c r="M86" t="n" s="6">
-        <v>46410</v>
+        <v>46392</v>
       </c>
       <c r="N86" t="s" s="1">
         <v>125</v>
@@ -9574,10 +9604,10 @@
         <v>46231</v>
       </c>
       <c r="L87" t="n" s="6">
-        <v>46239</v>
+        <v>46258</v>
       </c>
       <c r="M87" t="n" s="6">
-        <v>46391</v>
+        <v>46410</v>
       </c>
       <c r="N87" t="s" s="1">
         <v>125</v>
@@ -9656,19 +9686,19 @@
         <v>124</v>
       </c>
       <c r="K88" t="n" s="6">
-        <v>46295</v>
+        <v>46231</v>
       </c>
       <c r="L88" t="n" s="6">
-        <v>46300</v>
+        <v>46239</v>
       </c>
       <c r="M88" t="n" s="6">
-        <v>46387</v>
+        <v>46391</v>
       </c>
       <c r="N88" t="s" s="1">
         <v>125</v>
       </c>
       <c r="O88" t="n" s="3">
-        <v>4586.67</v>
+        <v>14000</v>
       </c>
       <c r="P88" t="n" s="3">
         <v>0</v>
@@ -9677,7 +9707,7 @@
         <v>0</v>
       </c>
       <c r="R88" t="n" s="3">
-        <v>4586.67</v>
+        <v>14000</v>
       </c>
       <c r="S88" s="2"/>
       <c r="T88" t="s" s="2">
@@ -9744,7 +9774,7 @@
         <v>46296</v>
       </c>
       <c r="L89" t="n" s="6">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="M89" t="n" s="6">
         <v>46387</v>
@@ -9753,7 +9783,7 @@
         <v>125</v>
       </c>
       <c r="O89" t="n" s="3">
-        <v>4533.33</v>
+        <v>4426.67</v>
       </c>
       <c r="P89" t="n" s="3">
         <v>0</v>
@@ -9762,7 +9792,7 @@
         <v>0</v>
       </c>
       <c r="R89" t="n" s="3">
-        <v>4533.33</v>
+        <v>4426.67</v>
       </c>
       <c r="S89" s="2"/>
       <c r="T89" t="s" s="2">
@@ -9796,6 +9826,176 @@
       <c r="AH89" s="2"/>
       <c r="AI89" s="4"/>
     </row>
+    <row r="90" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A90" t="s" s="1">
+        <v>572</v>
+      </c>
+      <c r="B90" t="s" s="1">
+        <v>573</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="D90" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="E90" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="F90" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="G90" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="I90" s="2"/>
+      <c r="J90" t="s" s="1">
+        <v>124</v>
+      </c>
+      <c r="K90" t="n" s="6">
+        <v>46295</v>
+      </c>
+      <c r="L90" t="n" s="6">
+        <v>46300</v>
+      </c>
+      <c r="M90" t="n" s="6">
+        <v>46387</v>
+      </c>
+      <c r="N90" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="O90" t="n" s="3">
+        <v>4586.67</v>
+      </c>
+      <c r="P90" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n" s="3">
+        <v>4586.67</v>
+      </c>
+      <c r="S90" s="2"/>
+      <c r="T90" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="U90" s="2"/>
+      <c r="V90" t="n" s="2">
+        <v>9968</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="Z90" t="n" s="1">
+        <v>10101</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AB90" s="2"/>
+      <c r="AC90" s="4"/>
+      <c r="AD90" s="2"/>
+      <c r="AE90" s="4"/>
+      <c r="AF90" s="2"/>
+      <c r="AG90" s="4"/>
+      <c r="AH90" s="2"/>
+      <c r="AI90" s="4"/>
+    </row>
+    <row r="91" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A91" t="s" s="1">
+        <v>577</v>
+      </c>
+      <c r="B91" t="s" s="1">
+        <v>578</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="D91" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="E91" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="F91" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="G91" t="s" s="1">
+        <v>122</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="I91" s="2"/>
+      <c r="J91" t="s" s="1">
+        <v>124</v>
+      </c>
+      <c r="K91" t="n" s="6">
+        <v>46296</v>
+      </c>
+      <c r="L91" t="n" s="6">
+        <v>46301</v>
+      </c>
+      <c r="M91" t="n" s="6">
+        <v>46387</v>
+      </c>
+      <c r="N91" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="O91" t="n" s="3">
+        <v>4533.33</v>
+      </c>
+      <c r="P91" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n" s="3">
+        <v>4533.33</v>
+      </c>
+      <c r="S91" s="2"/>
+      <c r="T91" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="U91" s="2"/>
+      <c r="V91" t="n" s="2">
+        <v>9968</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="Z91" t="n" s="1">
+        <v>10101</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AB91" s="2"/>
+      <c r="AC91" s="4"/>
+      <c r="AD91" s="2"/>
+      <c r="AE91" s="4"/>
+      <c r="AF91" s="2"/>
+      <c r="AG91" s="4"/>
+      <c r="AH91" s="2"/>
+      <c r="AI91" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9803,7 +10003,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K145"/>
+  <dimension ref="A1:K156"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="1" customWidth="1"/>
@@ -9867,10 +10067,10 @@
         <v>118</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="G2" t="s" s="1">
         <v>125</v>
@@ -9902,10 +10102,10 @@
         <v>118</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="G3" t="s" s="1">
         <v>125</v>
@@ -9937,10 +10137,10 @@
         <v>131</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="G4" t="s" s="1">
         <v>125</v>
@@ -9972,10 +10172,10 @@
         <v>139</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="G5" t="s" s="1">
         <v>125</v>
@@ -10007,10 +10207,10 @@
         <v>139</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="G6" t="s" s="1">
         <v>125</v>
@@ -10042,10 +10242,10 @@
         <v>144</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G7" t="s" s="1">
         <v>125</v>
@@ -10077,10 +10277,10 @@
         <v>144</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G8" t="s" s="1">
         <v>125</v>
@@ -10112,10 +10312,10 @@
         <v>153</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G9" t="s" s="1">
         <v>125</v>
@@ -10147,10 +10347,10 @@
         <v>153</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G10" t="s" s="1">
         <v>125</v>
@@ -10182,10 +10382,10 @@
         <v>158</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G11" t="s" s="1">
         <v>125</v>
@@ -10217,10 +10417,10 @@
         <v>158</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G12" t="s" s="1">
         <v>125</v>
@@ -10252,10 +10452,10 @@
         <v>163</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G13" t="s" s="1">
         <v>125</v>
@@ -10287,10 +10487,10 @@
         <v>163</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G14" t="s" s="1">
         <v>125</v>
@@ -10322,10 +10522,10 @@
         <v>168</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F15" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G15" t="s" s="1">
         <v>125</v>
@@ -10357,16 +10557,16 @@
         <v>168</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F16" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G16" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H16" t="n" s="3">
-        <v>14963</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n" s="3">
         <v>0</v>
@@ -10375,7 +10575,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n" s="3">
-        <v>14963</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -10392,16 +10592,16 @@
         <v>168</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G17" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H17" t="n" s="3">
-        <v>0</v>
+        <v>14963</v>
       </c>
       <c r="I17" t="n" s="3">
         <v>0</v>
@@ -10410,7 +10610,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n" s="3">
-        <v>0</v>
+        <v>14963</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -10427,10 +10627,10 @@
         <v>173</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G18" t="s" s="1">
         <v>125</v>
@@ -10462,10 +10662,10 @@
         <v>173</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G19" t="s" s="1">
         <v>125</v>
@@ -10488,25 +10688,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s" s="1">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C20" t="s" s="1">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F20" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G20" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H20" t="n" s="3">
-        <v>8307</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n" s="3">
         <v>0</v>
@@ -10515,7 +10715,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n" s="3">
-        <v>8307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
@@ -10523,25 +10723,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s" s="1">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C21" t="s" s="1">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F21" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G21" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H21" t="n" s="3">
-        <v>10564</v>
+        <v>8307</v>
       </c>
       <c r="I21" t="n" s="3">
         <v>0</v>
@@ -10550,7 +10750,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n" s="3">
-        <v>10564</v>
+        <v>8307</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
@@ -10558,25 +10758,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="s" s="1">
+        <v>182</v>
+      </c>
+      <c r="C22" t="s" s="1">
         <v>183</v>
       </c>
-      <c r="C22" t="s" s="1">
+      <c r="D22" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="D22" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="E22" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F22" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G22" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H22" t="n" s="3">
-        <v>0</v>
+        <v>10564</v>
       </c>
       <c r="I22" t="n" s="3">
         <v>0</v>
@@ -10585,7 +10785,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n" s="3">
-        <v>0</v>
+        <v>10564</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
@@ -10593,25 +10793,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="s" s="1">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s" s="1">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F23" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G23" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H23" t="n" s="3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n" s="3">
         <v>0</v>
@@ -10620,7 +10820,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n" s="3">
-        <v>15000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
@@ -10628,25 +10828,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="1">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C24" t="s" s="1">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F24" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G24" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H24" t="n" s="3">
-        <v>14961</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n" s="3">
         <v>0</v>
@@ -10655,7 +10855,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n" s="3">
-        <v>14961</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
@@ -10663,25 +10863,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="s" s="1">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C25" t="s" s="1">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F25" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G25" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H25" t="n" s="3">
-        <v>14444</v>
+        <v>15000</v>
       </c>
       <c r="I25" t="n" s="3">
         <v>0</v>
@@ -10690,7 +10890,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n" s="3">
-        <v>14444</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
@@ -10698,25 +10898,25 @@
         <v>25</v>
       </c>
       <c r="B26" t="s" s="1">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="C26" t="s" s="1">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F26" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G26" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H26" t="n" s="3">
-        <v>10389</v>
+        <v>14961</v>
       </c>
       <c r="I26" t="n" s="3">
         <v>0</v>
@@ -10725,7 +10925,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n" s="3">
-        <v>10389</v>
+        <v>14961</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
@@ -10733,25 +10933,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="s" s="1">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="C27" t="s" s="1">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F27" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G27" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H27" t="n" s="3">
-        <v>14333</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n" s="3">
         <v>0</v>
@@ -10760,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n" s="3">
-        <v>14333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
@@ -10768,25 +10968,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="s" s="1">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="C28" t="s" s="1">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F28" t="s" s="2">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G28" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H28" t="n" s="3">
-        <v>14500</v>
+        <v>14444</v>
       </c>
       <c r="I28" t="n" s="3">
         <v>0</v>
@@ -10795,7 +10995,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n" s="3">
-        <v>14500</v>
+        <v>14444</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
@@ -10803,25 +11003,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="s" s="1">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="C29" t="s" s="1">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F29" t="s" s="2">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="G29" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H29" t="n" s="3">
-        <v>27000</v>
+        <v>10389</v>
       </c>
       <c r="I29" t="n" s="3">
         <v>0</v>
@@ -10830,7 +11030,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n" s="3">
-        <v>27000</v>
+        <v>10389</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
@@ -10838,25 +11038,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="s" s="1">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="C30" t="s" s="1">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F30" t="s" s="2">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="G30" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H30" t="n" s="3">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n" s="3">
         <v>0</v>
@@ -10865,7 +11065,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n" s="3">
-        <v>27000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
@@ -10873,25 +11073,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="s" s="1">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="C31" t="s" s="1">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F31" t="s" s="2">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="G31" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H31" t="n" s="3">
-        <v>9600</v>
+        <v>14333</v>
       </c>
       <c r="I31" t="n" s="3">
         <v>0</v>
@@ -10900,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n" s="3">
-        <v>9600</v>
+        <v>14333</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
@@ -10908,25 +11108,25 @@
         <v>31</v>
       </c>
       <c r="B32" t="s" s="1">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="C32" t="s" s="1">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F32" t="s" s="2">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="G32" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H32" t="n" s="3">
-        <v>0</v>
+        <v>14500</v>
       </c>
       <c r="I32" t="n" s="3">
         <v>0</v>
@@ -10935,7 +11135,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n" s="3">
-        <v>0</v>
+        <v>14500</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
@@ -10943,25 +11143,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="s" s="1">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C33" t="s" s="1">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F33" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="G33" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H33" t="n" s="3">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I33" t="n" s="3">
         <v>0</v>
@@ -10970,7 +11170,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n" s="3">
-        <v>0</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
@@ -10978,25 +11178,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="s" s="1">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C34" t="s" s="1">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F34" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="G34" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H34" t="n" s="3">
-        <v>9600</v>
+        <v>27000</v>
       </c>
       <c r="I34" t="n" s="3">
         <v>0</v>
@@ -11005,7 +11205,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n" s="3">
-        <v>9600</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
@@ -11013,25 +11213,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="s" s="1">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C35" t="s" s="1">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G35" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H35" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I35" t="n" s="3">
         <v>0</v>
@@ -11040,7 +11240,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
@@ -11048,19 +11248,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="s" s="1">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C36" t="s" s="1">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="G36" t="s" s="1">
         <v>125</v>
@@ -11083,19 +11283,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="s" s="1">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C37" t="s" s="1">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="G37" t="s" s="1">
         <v>125</v>
@@ -11118,19 +11318,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s" s="1">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C38" t="s" s="1">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G38" t="s" s="1">
         <v>125</v>
@@ -11153,25 +11353,25 @@
         <v>38</v>
       </c>
       <c r="B39" t="s" s="1">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C39" t="s" s="1">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F39" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G39" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H39" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n" s="3">
         <v>0</v>
@@ -11180,7 +11380,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
@@ -11188,25 +11388,25 @@
         <v>39</v>
       </c>
       <c r="B40" t="s" s="1">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C40" t="s" s="1">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="G40" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H40" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n" s="3">
         <v>0</v>
@@ -11215,7 +11415,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
@@ -11223,25 +11423,25 @@
         <v>40</v>
       </c>
       <c r="B41" t="s" s="1">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C41" t="s" s="1">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="G41" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H41" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I41" t="n" s="3">
         <v>0</v>
@@ -11250,7 +11450,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
@@ -11258,19 +11458,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="s" s="1">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C42" t="s" s="1">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F42" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G42" t="s" s="1">
         <v>125</v>
@@ -11293,19 +11493,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s" s="1">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C43" t="s" s="1">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G43" t="s" s="1">
         <v>125</v>
@@ -11328,19 +11528,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s" s="1">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C44" t="s" s="1">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G44" t="s" s="1">
         <v>125</v>
@@ -11363,25 +11563,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="s" s="1">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="C45" t="s" s="1">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G45" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H45" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n" s="3">
         <v>0</v>
@@ -11390,7 +11590,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
@@ -11398,19 +11598,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="s" s="1">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C46" t="s" s="1">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G46" t="s" s="1">
         <v>125</v>
@@ -11433,25 +11633,25 @@
         <v>46</v>
       </c>
       <c r="B47" t="s" s="1">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="C47" t="s" s="1">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F47" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G47" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H47" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I47" t="n" s="3">
         <v>0</v>
@@ -11460,7 +11660,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
@@ -11468,19 +11668,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="s" s="1">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="C48" t="s" s="1">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F48" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G48" t="s" s="1">
         <v>125</v>
@@ -11503,19 +11703,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="s" s="1">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C49" t="s" s="1">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F49" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G49" t="s" s="1">
         <v>125</v>
@@ -11538,19 +11738,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="s" s="1">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C50" t="s" s="1">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F50" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G50" t="s" s="1">
         <v>125</v>
@@ -11573,19 +11773,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="s" s="1">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C51" t="s" s="1">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F51" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G51" t="s" s="1">
         <v>125</v>
@@ -11608,19 +11808,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="s" s="1">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C52" t="s" s="1">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G52" t="s" s="1">
         <v>125</v>
@@ -11643,19 +11843,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s" s="1">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="C53" t="s" s="1">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F53" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G53" t="s" s="1">
         <v>125</v>
@@ -11678,19 +11878,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s" s="1">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="C54" t="s" s="1">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G54" t="s" s="1">
         <v>125</v>
@@ -11713,19 +11913,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s" s="1">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="C55" t="s" s="1">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F55" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G55" t="s" s="1">
         <v>125</v>
@@ -11748,25 +11948,25 @@
         <v>55</v>
       </c>
       <c r="B56" t="s" s="1">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="C56" t="s" s="1">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F56" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G56" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H56" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n" s="3">
         <v>0</v>
@@ -11775,7 +11975,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
@@ -11783,25 +11983,25 @@
         <v>56</v>
       </c>
       <c r="B57" t="s" s="1">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="C57" t="s" s="1">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F57" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G57" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H57" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I57" t="n" s="3">
         <v>0</v>
@@ -11810,7 +12010,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
@@ -11818,25 +12018,25 @@
         <v>57</v>
       </c>
       <c r="B58" t="s" s="1">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C58" t="s" s="1">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F58" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G58" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H58" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n" s="3">
         <v>0</v>
@@ -11845,7 +12045,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
@@ -11853,19 +12053,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s" s="1">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="C59" t="s" s="1">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F59" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G59" t="s" s="1">
         <v>125</v>
@@ -11888,25 +12088,25 @@
         <v>59</v>
       </c>
       <c r="B60" t="s" s="1">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C60" t="s" s="1">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F60" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G60" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H60" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I60" t="n" s="3">
         <v>0</v>
@@ -11915,7 +12115,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
@@ -11923,19 +12123,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s" s="1">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C61" t="s" s="1">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F61" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G61" t="s" s="1">
         <v>125</v>
@@ -11958,19 +12158,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="s" s="1">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C62" t="s" s="1">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F62" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G62" t="s" s="1">
         <v>125</v>
@@ -11993,19 +12193,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="s" s="1">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C63" t="s" s="1">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F63" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G63" t="s" s="1">
         <v>125</v>
@@ -12028,19 +12228,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s" s="1">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C64" t="s" s="1">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F64" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G64" t="s" s="1">
         <v>125</v>
@@ -12063,25 +12263,25 @@
         <v>64</v>
       </c>
       <c r="B65" t="s" s="1">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C65" t="s" s="1">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F65" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G65" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H65" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I65" t="n" s="3">
         <v>0</v>
@@ -12090,7 +12290,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
@@ -12098,25 +12298,25 @@
         <v>65</v>
       </c>
       <c r="B66" t="s" s="1">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C66" t="s" s="1">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F66" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G66" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H66" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n" s="3">
         <v>0</v>
@@ -12125,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
@@ -12133,19 +12333,19 @@
         <v>66</v>
       </c>
       <c r="B67" t="s" s="1">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C67" t="s" s="1">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F67" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G67" t="s" s="1">
         <v>125</v>
@@ -12168,19 +12368,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="s" s="1">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C68" t="s" s="1">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="D68" t="s" s="2">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G68" t="s" s="1">
         <v>125</v>
@@ -12203,19 +12403,19 @@
         <v>68</v>
       </c>
       <c r="B69" t="s" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C69" t="s" s="1">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="D69" t="s" s="2">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F69" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G69" t="s" s="1">
         <v>125</v>
@@ -12238,19 +12438,19 @@
         <v>69</v>
       </c>
       <c r="B70" t="s" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C70" t="s" s="1">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="D70" t="s" s="2">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F70" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G70" t="s" s="1">
         <v>125</v>
@@ -12273,25 +12473,25 @@
         <v>70</v>
       </c>
       <c r="B71" t="s" s="1">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C71" t="s" s="1">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="D71" t="s" s="2">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F71" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G71" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H71" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I71" t="n" s="3">
         <v>0</v>
@@ -12300,7 +12500,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
@@ -12308,25 +12508,25 @@
         <v>71</v>
       </c>
       <c r="B72" t="s" s="1">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C72" t="s" s="1">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="D72" t="s" s="2">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F72" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G72" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H72" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n" s="3">
         <v>0</v>
@@ -12335,7 +12535,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
@@ -12343,19 +12543,19 @@
         <v>72</v>
       </c>
       <c r="B73" t="s" s="1">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C73" t="s" s="1">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="D73" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F73" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G73" t="s" s="1">
         <v>125</v>
@@ -12378,25 +12578,25 @@
         <v>73</v>
       </c>
       <c r="B74" t="s" s="1">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="C74" t="s" s="1">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="D74" t="s" s="2">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F74" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G74" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H74" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n" s="3">
         <v>0</v>
@@ -12405,7 +12605,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
@@ -12413,19 +12613,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s" s="1">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C75" t="s" s="1">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="D75" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G75" t="s" s="1">
         <v>125</v>
@@ -12448,25 +12648,25 @@
         <v>75</v>
       </c>
       <c r="B76" t="s" s="1">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="C76" t="s" s="1">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="D76" t="s" s="2">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F76" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G76" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H76" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I76" t="n" s="3">
         <v>0</v>
@@ -12475,7 +12675,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
@@ -12483,19 +12683,19 @@
         <v>76</v>
       </c>
       <c r="B77" t="s" s="1">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C77" t="s" s="1">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D77" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F77" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G77" t="s" s="1">
         <v>125</v>
@@ -12518,19 +12718,19 @@
         <v>77</v>
       </c>
       <c r="B78" t="s" s="1">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="C78" t="s" s="1">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="D78" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F78" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G78" t="s" s="1">
         <v>125</v>
@@ -12553,19 +12753,19 @@
         <v>78</v>
       </c>
       <c r="B79" t="s" s="1">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="C79" t="s" s="1">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="D79" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F79" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G79" t="s" s="1">
         <v>125</v>
@@ -12588,25 +12788,25 @@
         <v>79</v>
       </c>
       <c r="B80" t="s" s="1">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C80" t="s" s="1">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D80" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F80" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G80" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H80" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I80" t="n" s="3">
         <v>0</v>
@@ -12615,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
@@ -12623,25 +12823,25 @@
         <v>80</v>
       </c>
       <c r="B81" t="s" s="1">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C81" t="s" s="1">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D81" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F81" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G81" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H81" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n" s="3">
         <v>0</v>
@@ -12650,7 +12850,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
@@ -12658,25 +12858,25 @@
         <v>81</v>
       </c>
       <c r="B82" t="s" s="1">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C82" t="s" s="1">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="D82" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F82" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G82" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H82" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n" s="3">
         <v>0</v>
@@ -12685,7 +12885,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
@@ -12693,25 +12893,25 @@
         <v>82</v>
       </c>
       <c r="B83" t="s" s="1">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C83" t="s" s="1">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="D83" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G83" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H83" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I83" t="n" s="3">
         <v>0</v>
@@ -12720,7 +12920,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
@@ -12728,19 +12928,19 @@
         <v>83</v>
       </c>
       <c r="B84" t="s" s="1">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C84" t="s" s="1">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="D84" t="s" s="2">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G84" t="s" s="1">
         <v>125</v>
@@ -12763,25 +12963,25 @@
         <v>84</v>
       </c>
       <c r="B85" t="s" s="1">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C85" t="s" s="1">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="D85" t="s" s="2">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F85" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G85" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H85" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n" s="3">
         <v>0</v>
@@ -12790,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
@@ -12798,19 +12998,19 @@
         <v>85</v>
       </c>
       <c r="B86" t="s" s="1">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C86" t="s" s="1">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="D86" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F86" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G86" t="s" s="1">
         <v>125</v>
@@ -12833,19 +13033,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="s" s="1">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="C87" t="s" s="1">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="D87" t="s" s="2">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F87" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G87" t="s" s="1">
         <v>125</v>
@@ -12868,19 +13068,19 @@
         <v>87</v>
       </c>
       <c r="B88" t="s" s="1">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C88" t="s" s="1">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F88" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G88" t="s" s="1">
         <v>125</v>
@@ -12903,19 +13103,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s" s="1">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="C89" t="s" s="1">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="D89" t="s" s="2">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F89" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G89" t="s" s="1">
         <v>125</v>
@@ -12938,25 +13138,25 @@
         <v>89</v>
       </c>
       <c r="B90" t="s" s="1">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="C90" t="s" s="1">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="D90" t="s" s="2">
-        <v>387</v>
+        <v>367</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F90" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G90" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H90" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n" s="3">
         <v>0</v>
@@ -12965,7 +13165,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
@@ -12973,25 +13173,25 @@
         <v>90</v>
       </c>
       <c r="B91" t="s" s="1">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="C91" t="s" s="1">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="D91" t="s" s="2">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F91" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G91" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H91" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I91" t="n" s="3">
         <v>0</v>
@@ -13000,7 +13200,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
@@ -13008,25 +13208,25 @@
         <v>91</v>
       </c>
       <c r="B92" t="s" s="1">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="C92" t="s" s="1">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="D92" t="s" s="2">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F92" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G92" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H92" t="n" s="3">
-        <v>19200</v>
+        <v>9600</v>
       </c>
       <c r="I92" t="n" s="3">
         <v>0</v>
@@ -13035,7 +13235,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n" s="3">
-        <v>19200</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
@@ -13043,25 +13243,25 @@
         <v>92</v>
       </c>
       <c r="B93" t="s" s="1">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C93" t="s" s="1">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D93" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F93" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G93" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H93" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="I93" t="n" s="3">
         <v>0</v>
@@ -13070,7 +13270,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
@@ -13078,25 +13278,25 @@
         <v>93</v>
       </c>
       <c r="B94" t="s" s="1">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="C94" t="s" s="1">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="D94" t="s" s="2">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F94" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G94" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H94" t="n" s="3">
-        <v>19500</v>
+        <v>9600</v>
       </c>
       <c r="I94" t="n" s="3">
         <v>0</v>
@@ -13105,7 +13305,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n" s="3">
-        <v>19500</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
@@ -13113,25 +13313,25 @@
         <v>94</v>
       </c>
       <c r="B95" t="s" s="1">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="C95" t="s" s="1">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="D95" t="s" s="2">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F95" t="s" s="2">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="G95" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H95" t="n" s="3">
-        <v>32218.67</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n" s="3">
         <v>0</v>
@@ -13140,7 +13340,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n" s="3">
-        <v>32218.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
@@ -13148,25 +13348,25 @@
         <v>95</v>
       </c>
       <c r="B96" t="s" s="1">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="C96" t="s" s="1">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="D96" t="s" s="2">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G96" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H96" t="n" s="3">
-        <v>0</v>
+        <v>19200</v>
       </c>
       <c r="I96" t="n" s="3">
         <v>0</v>
@@ -13175,7 +13375,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n" s="3">
-        <v>0</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.3">
@@ -13183,25 +13383,25 @@
         <v>96</v>
       </c>
       <c r="B97" t="s" s="1">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="C97" t="s" s="1">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="D97" t="s" s="2">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F97" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G97" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H97" t="n" s="3">
-        <v>19200</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n" s="3">
         <v>0</v>
@@ -13210,7 +13410,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n" s="3">
-        <v>19200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
@@ -13218,25 +13418,25 @@
         <v>97</v>
       </c>
       <c r="B98" t="s" s="1">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C98" t="s" s="1">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="D98" t="s" s="2">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F98" t="s" s="2">
-        <v>573</v>
+        <v>589</v>
       </c>
       <c r="G98" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H98" t="n" s="3">
-        <v>550500</v>
+        <v>19500</v>
       </c>
       <c r="I98" t="n" s="3">
         <v>0</v>
@@ -13245,7 +13445,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n" s="3">
-        <v>550500</v>
+        <v>19500</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
@@ -13253,25 +13453,25 @@
         <v>98</v>
       </c>
       <c r="B99" t="s" s="1">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="C99" t="s" s="1">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="D99" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F99" t="s" s="2">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="G99" t="s" s="1">
-        <v>419</v>
+        <v>125</v>
       </c>
       <c r="H99" t="n" s="3">
-        <v>1610690000</v>
+        <v>32218.67</v>
       </c>
       <c r="I99" t="n" s="3">
         <v>0</v>
@@ -13280,7 +13480,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n" s="3">
-        <v>1610690000</v>
+        <v>32218.67</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
@@ -13288,25 +13488,25 @@
         <v>99</v>
       </c>
       <c r="B100" t="s" s="1">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="C100" t="s" s="1">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="D100" t="s" s="2">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="F100" t="s" s="2">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="G100" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H100" t="n" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="I100" t="n" s="3">
         <v>0</v>
@@ -13315,7 +13515,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n" s="3">
-        <v>30000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
@@ -13323,25 +13523,25 @@
         <v>100</v>
       </c>
       <c r="B101" t="s" s="1">
-        <v>428</v>
+        <v>407</v>
       </c>
       <c r="C101" t="s" s="1">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="D101" t="s" s="2">
-        <v>430</v>
+        <v>409</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="F101" t="s" s="2">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="G101" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H101" t="n" s="3">
-        <v>15000</v>
+        <v>19200</v>
       </c>
       <c r="I101" t="n" s="3">
         <v>0</v>
@@ -13350,7 +13550,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n" s="3">
-        <v>15000</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
@@ -13358,25 +13558,25 @@
         <v>101</v>
       </c>
       <c r="B102" t="s" s="1">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="C102" t="s" s="1">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="F102" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="G102" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H102" t="n" s="3">
-        <v>54000</v>
+        <v>550500</v>
       </c>
       <c r="I102" t="n" s="3">
         <v>0</v>
@@ -13385,7 +13585,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n" s="3">
-        <v>54000</v>
+        <v>550500</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
@@ -13393,25 +13593,25 @@
         <v>102</v>
       </c>
       <c r="B103" t="s" s="1">
-        <v>437</v>
+        <v>412</v>
       </c>
       <c r="C103" t="s" s="1">
-        <v>438</v>
+        <v>413</v>
       </c>
       <c r="D103" t="s" s="2">
-        <v>439</v>
+        <v>414</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="G103" t="s" s="1">
-        <v>125</v>
+        <v>422</v>
       </c>
       <c r="H103" t="n" s="3">
-        <v>6552</v>
+        <v>1610690000</v>
       </c>
       <c r="I103" t="n" s="3">
         <v>0</v>
@@ -13420,7 +13620,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n" s="3">
-        <v>6552</v>
+        <v>1610690000</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
@@ -13428,25 +13628,25 @@
         <v>103</v>
       </c>
       <c r="B104" t="s" s="1">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="C104" t="s" s="1">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="D104" t="s" s="2">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="F104" t="s" s="2">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="G104" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H104" t="n" s="3">
-        <v>6552</v>
+        <v>30000</v>
       </c>
       <c r="I104" t="n" s="3">
         <v>0</v>
@@ -13455,7 +13655,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="n" s="3">
-        <v>6552</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.3">
@@ -13463,25 +13663,25 @@
         <v>104</v>
       </c>
       <c r="B105" t="s" s="1">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="C105" t="s" s="1">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F105" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="G105" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H105" t="n" s="3">
-        <v>13104</v>
+        <v>15000</v>
       </c>
       <c r="I105" t="n" s="3">
         <v>0</v>
@@ -13490,7 +13690,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="n" s="3">
-        <v>13104</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.3">
@@ -13498,25 +13698,25 @@
         <v>105</v>
       </c>
       <c r="B106" t="s" s="1">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C106" t="s" s="1">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D106" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="F106" t="s" s="2">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="G106" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H106" t="n" s="3">
-        <v>6552</v>
+        <v>54000</v>
       </c>
       <c r="I106" t="n" s="3">
         <v>0</v>
@@ -13525,7 +13725,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n" s="3">
-        <v>6552</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
@@ -13542,16 +13742,16 @@
         <v>439</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="F107" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="G107" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H107" t="n" s="3">
-        <v>2808</v>
+        <v>6552</v>
       </c>
       <c r="I107" t="n" s="3">
         <v>0</v>
@@ -13560,7 +13760,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="n" s="3">
-        <v>2808</v>
+        <v>6552</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
@@ -13577,16 +13777,16 @@
         <v>439</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="F108" t="s" s="2">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="G108" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H108" t="n" s="3">
-        <v>2808</v>
+        <v>6552</v>
       </c>
       <c r="I108" t="n" s="3">
         <v>0</v>
@@ -13595,7 +13795,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="n" s="3">
-        <v>2808</v>
+        <v>6552</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.3">
@@ -13612,16 +13812,16 @@
         <v>439</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="G109" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H109" t="n" s="3">
-        <v>2808</v>
+        <v>13104</v>
       </c>
       <c r="I109" t="n" s="3">
         <v>0</v>
@@ -13630,7 +13830,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="n" s="3">
-        <v>2808</v>
+        <v>13104</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
@@ -13647,16 +13847,16 @@
         <v>439</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="F110" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="G110" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H110" t="n" s="3">
-        <v>2808</v>
+        <v>6552</v>
       </c>
       <c r="I110" t="n" s="3">
         <v>0</v>
@@ -13665,7 +13865,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n" s="3">
-        <v>2808</v>
+        <v>6552</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
@@ -13682,10 +13882,10 @@
         <v>439</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="F111" t="s" s="2">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="G111" t="s" s="1">
         <v>125</v>
@@ -13708,25 +13908,25 @@
         <v>111</v>
       </c>
       <c r="B112" t="s" s="1">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C112" t="s" s="1">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D112" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F112" t="s" s="2">
-        <v>579</v>
+        <v>594</v>
       </c>
       <c r="G112" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H112" t="n" s="3">
-        <v>6400</v>
+        <v>2808</v>
       </c>
       <c r="I112" t="n" s="3">
         <v>0</v>
@@ -13735,7 +13935,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="n" s="3">
-        <v>6400</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
@@ -13743,25 +13943,25 @@
         <v>112</v>
       </c>
       <c r="B113" t="s" s="1">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C113" t="s" s="1">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D113" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F113" t="s" s="2">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="G113" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H113" t="n" s="3">
-        <v>0</v>
+        <v>2808</v>
       </c>
       <c r="I113" t="n" s="3">
         <v>0</v>
@@ -13770,7 +13970,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="n" s="3">
-        <v>0</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
@@ -13778,25 +13978,25 @@
         <v>113</v>
       </c>
       <c r="B114" t="s" s="1">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C114" t="s" s="1">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="D114" t="s" s="2">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F114" t="s" s="2">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="G114" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H114" t="n" s="3">
-        <v>0</v>
+        <v>2808</v>
       </c>
       <c r="I114" t="n" s="3">
         <v>0</v>
@@ -13805,7 +14005,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="n" s="3">
-        <v>0</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
@@ -13813,25 +14013,25 @@
         <v>114</v>
       </c>
       <c r="B115" t="s" s="1">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="C115" t="s" s="1">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="D115" t="s" s="2">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="F115" t="s" s="2">
-        <v>579</v>
+        <v>595</v>
       </c>
       <c r="G115" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H115" t="n" s="3">
-        <v>6400</v>
+        <v>2808</v>
       </c>
       <c r="I115" t="n" s="3">
         <v>0</v>
@@ -13840,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="n" s="3">
-        <v>6400</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
@@ -13848,19 +14048,19 @@
         <v>115</v>
       </c>
       <c r="B116" t="s" s="1">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C116" t="s" s="1">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="D116" t="s" s="2">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F116" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G116" t="s" s="1">
         <v>125</v>
@@ -13883,19 +14083,19 @@
         <v>116</v>
       </c>
       <c r="B117" t="s" s="1">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C117" t="s" s="1">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="D117" t="s" s="2">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="E117" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F117" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G117" t="s" s="1">
         <v>125</v>
@@ -13918,19 +14118,19 @@
         <v>117</v>
       </c>
       <c r="B118" t="s" s="1">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="C118" t="s" s="1">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D118" t="s" s="2">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="E118" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F118" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G118" t="s" s="1">
         <v>125</v>
@@ -13953,19 +14153,19 @@
         <v>118</v>
       </c>
       <c r="B119" t="s" s="1">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="C119" t="s" s="1">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D119" t="s" s="2">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="E119" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F119" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G119" t="s" s="1">
         <v>125</v>
@@ -13988,25 +14188,25 @@
         <v>119</v>
       </c>
       <c r="B120" t="s" s="1">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="C120" t="s" s="1">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="D120" t="s" s="2">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F120" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G120" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H120" t="n" s="3">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n" s="3">
         <v>0</v>
@@ -14015,7 +14215,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="n" s="3">
-        <v>6400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.3">
@@ -14023,19 +14223,19 @@
         <v>120</v>
       </c>
       <c r="B121" t="s" s="1">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="C121" t="s" s="1">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="E121" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F121" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G121" t="s" s="1">
         <v>125</v>
@@ -14058,19 +14258,19 @@
         <v>121</v>
       </c>
       <c r="B122" t="s" s="1">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="C122" t="s" s="1">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F122" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G122" t="s" s="1">
         <v>125</v>
@@ -14093,19 +14293,19 @@
         <v>122</v>
       </c>
       <c r="B123" t="s" s="1">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="C123" t="s" s="1">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="D123" t="s" s="2">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="E123" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F123" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G123" t="s" s="1">
         <v>125</v>
@@ -14128,25 +14328,25 @@
         <v>123</v>
       </c>
       <c r="B124" t="s" s="1">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="C124" t="s" s="1">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="D124" t="s" s="2">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="E124" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F124" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="G124" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H124" t="n" s="3">
-        <v>6400</v>
+        <v>15000</v>
       </c>
       <c r="I124" t="n" s="3">
         <v>0</v>
@@ -14155,7 +14355,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="n" s="3">
-        <v>6400</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.3">
@@ -14163,19 +14363,19 @@
         <v>124</v>
       </c>
       <c r="B125" t="s" s="1">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="C125" t="s" s="1">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="D125" t="s" s="2">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="E125" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F125" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G125" t="s" s="1">
         <v>125</v>
@@ -14198,19 +14398,19 @@
         <v>125</v>
       </c>
       <c r="B126" t="s" s="1">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="C126" t="s" s="1">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="E126" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F126" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G126" t="s" s="1">
         <v>125</v>
@@ -14233,25 +14433,25 @@
         <v>126</v>
       </c>
       <c r="B127" t="s" s="1">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="C127" t="s" s="1">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="D127" t="s" s="2">
-        <v>494</v>
+        <v>474</v>
       </c>
       <c r="E127" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F127" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G127" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H127" t="n" s="3">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n" s="3">
         <v>0</v>
@@ -14260,7 +14460,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="n" s="3">
-        <v>6400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.3">
@@ -14268,25 +14468,25 @@
         <v>127</v>
       </c>
       <c r="B128" t="s" s="1">
-        <v>497</v>
+        <v>477</v>
       </c>
       <c r="C128" t="s" s="1">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="D128" t="s" s="2">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="E128" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F128" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G128" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H128" t="n" s="3">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n" s="3">
         <v>0</v>
@@ -14295,7 +14495,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="n" s="3">
-        <v>6400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.3">
@@ -14303,19 +14503,19 @@
         <v>128</v>
       </c>
       <c r="B129" t="s" s="1">
-        <v>502</v>
+        <v>477</v>
       </c>
       <c r="C129" t="s" s="1">
-        <v>503</v>
+        <v>478</v>
       </c>
       <c r="D129" t="s" s="2">
-        <v>504</v>
+        <v>479</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F129" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G129" t="s" s="1">
         <v>125</v>
@@ -14338,25 +14538,25 @@
         <v>129</v>
       </c>
       <c r="B130" t="s" s="1">
-        <v>507</v>
+        <v>482</v>
       </c>
       <c r="C130" t="s" s="1">
-        <v>508</v>
+        <v>483</v>
       </c>
       <c r="D130" t="s" s="2">
-        <v>509</v>
+        <v>484</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F130" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G130" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H130" t="n" s="3">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n" s="3">
         <v>0</v>
@@ -14365,7 +14565,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="n" s="3">
-        <v>6400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.3">
@@ -14373,25 +14573,25 @@
         <v>130</v>
       </c>
       <c r="B131" t="s" s="1">
-        <v>512</v>
+        <v>482</v>
       </c>
       <c r="C131" t="s" s="1">
-        <v>513</v>
+        <v>483</v>
       </c>
       <c r="D131" t="s" s="2">
-        <v>514</v>
+        <v>484</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F131" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G131" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H131" t="n" s="3">
-        <v>9600</v>
+        <v>6400</v>
       </c>
       <c r="I131" t="n" s="3">
         <v>0</v>
@@ -14400,7 +14600,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n" s="3">
-        <v>9600</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.3">
@@ -14408,25 +14608,25 @@
         <v>131</v>
       </c>
       <c r="B132" t="s" s="1">
-        <v>512</v>
+        <v>487</v>
       </c>
       <c r="C132" t="s" s="1">
-        <v>513</v>
+        <v>488</v>
       </c>
       <c r="D132" t="s" s="2">
-        <v>514</v>
+        <v>489</v>
       </c>
       <c r="E132" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F132" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G132" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H132" t="n" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="I132" t="n" s="3">
         <v>0</v>
@@ -14435,7 +14635,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.3">
@@ -14443,25 +14643,25 @@
         <v>132</v>
       </c>
       <c r="B133" t="s" s="1">
-        <v>517</v>
+        <v>492</v>
       </c>
       <c r="C133" t="s" s="1">
-        <v>518</v>
+        <v>493</v>
       </c>
       <c r="D133" t="s" s="2">
-        <v>519</v>
+        <v>494</v>
       </c>
       <c r="E133" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F133" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G133" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H133" t="n" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="I133" t="n" s="3">
         <v>0</v>
@@ -14470,7 +14670,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="n" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
@@ -14478,25 +14678,25 @@
         <v>133</v>
       </c>
       <c r="B134" t="s" s="1">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="C134" t="s" s="1">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="D134" t="s" s="2">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="E134" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F134" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G134" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H134" t="n" s="3">
-        <v>9600</v>
+        <v>6400</v>
       </c>
       <c r="I134" t="n" s="3">
         <v>0</v>
@@ -14505,7 +14705,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="n" s="3">
-        <v>9600</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.3">
@@ -14513,25 +14713,25 @@
         <v>134</v>
       </c>
       <c r="B135" t="s" s="1">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="C135" t="s" s="1">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="D135" t="s" s="2">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="E135" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F135" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G135" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H135" t="n" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="I135" t="n" s="3">
         <v>0</v>
@@ -14540,7 +14740,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="n" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.3">
@@ -14548,25 +14748,25 @@
         <v>135</v>
       </c>
       <c r="B136" t="s" s="1">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="C136" t="s" s="1">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="D136" t="s" s="2">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="E136" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F136" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G136" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H136" t="n" s="3">
-        <v>9600</v>
+        <v>6400</v>
       </c>
       <c r="I136" t="n" s="3">
         <v>0</v>
@@ -14575,7 +14775,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="n" s="3">
-        <v>9600</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.3">
@@ -14583,25 +14783,25 @@
         <v>136</v>
       </c>
       <c r="B137" t="s" s="1">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="C137" t="s" s="1">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="D137" t="s" s="2">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="E137" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F137" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G137" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H137" t="n" s="3">
-        <v>9600</v>
+        <v>6400</v>
       </c>
       <c r="I137" t="n" s="3">
         <v>0</v>
@@ -14610,7 +14810,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n" s="3">
-        <v>9600</v>
+        <v>6400</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.3">
@@ -14618,19 +14818,19 @@
         <v>137</v>
       </c>
       <c r="B138" t="s" s="1">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="C138" t="s" s="1">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="D138" t="s" s="2">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="E138" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F138" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G138" t="s" s="1">
         <v>125</v>
@@ -14653,25 +14853,25 @@
         <v>138</v>
       </c>
       <c r="B139" t="s" s="1">
-        <v>537</v>
+        <v>517</v>
       </c>
       <c r="C139" t="s" s="1">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="D139" t="s" s="2">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="E139" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F139" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G139" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H139" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n" s="3">
         <v>0</v>
@@ -14680,7 +14880,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="n" s="3">
-        <v>9600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.3">
@@ -14688,19 +14888,19 @@
         <v>139</v>
       </c>
       <c r="B140" t="s" s="1">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="C140" t="s" s="1">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="D140" t="s" s="2">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="E140" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F140" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G140" t="s" s="1">
         <v>125</v>
@@ -14723,25 +14923,25 @@
         <v>140</v>
       </c>
       <c r="B141" t="s" s="1">
-        <v>547</v>
+        <v>522</v>
       </c>
       <c r="C141" t="s" s="1">
-        <v>548</v>
+        <v>523</v>
       </c>
       <c r="D141" t="s" s="2">
-        <v>549</v>
+        <v>524</v>
       </c>
       <c r="E141" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F141" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G141" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H141" t="n" s="3">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n" s="3">
         <v>0</v>
@@ -14750,7 +14950,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n" s="3">
-        <v>14000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.3">
@@ -14758,25 +14958,25 @@
         <v>141</v>
       </c>
       <c r="B142" t="s" s="1">
-        <v>552</v>
+        <v>527</v>
       </c>
       <c r="C142" t="s" s="1">
-        <v>553</v>
+        <v>528</v>
       </c>
       <c r="D142" t="s" s="2">
-        <v>554</v>
+        <v>529</v>
       </c>
       <c r="E142" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F142" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G142" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H142" t="n" s="3">
-        <v>14000</v>
+        <v>9600</v>
       </c>
       <c r="I142" t="n" s="3">
         <v>0</v>
@@ -14785,7 +14985,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="n" s="3">
-        <v>14000</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.3">
@@ -14793,25 +14993,25 @@
         <v>142</v>
       </c>
       <c r="B143" t="s" s="1">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="C143" t="s" s="1">
-        <v>558</v>
+        <v>528</v>
       </c>
       <c r="D143" t="s" s="2">
-        <v>559</v>
+        <v>529</v>
       </c>
       <c r="E143" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F143" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G143" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H143" t="n" s="3">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n" s="3">
         <v>0</v>
@@ -14820,7 +15020,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="n" s="3">
-        <v>14000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.3">
@@ -14828,25 +15028,25 @@
         <v>143</v>
       </c>
       <c r="B144" t="s" s="1">
-        <v>562</v>
+        <v>532</v>
       </c>
       <c r="C144" t="s" s="1">
-        <v>563</v>
+        <v>533</v>
       </c>
       <c r="D144" t="s" s="2">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="E144" t="s" s="2">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="F144" t="s" s="2">
-        <v>579</v>
+        <v>589</v>
       </c>
       <c r="G144" t="s" s="1">
         <v>125</v>
       </c>
       <c r="H144" t="n" s="3">
-        <v>4586.67</v>
+        <v>9600</v>
       </c>
       <c r="I144" t="n" s="3">
         <v>0</v>
@@ -14855,7 +15055,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="n" s="3">
-        <v>4586.67</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.3">
@@ -14863,33 +15063,418 @@
         <v>144</v>
       </c>
       <c r="B145" t="s" s="1">
+        <v>537</v>
+      </c>
+      <c r="C145" t="s" s="1">
+        <v>538</v>
+      </c>
+      <c r="D145" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="E145" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="F145" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="G145" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="H145" t="n" s="3">
+        <v>9600</v>
+      </c>
+      <c r="I145" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n" s="3">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A146" t="n" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146" t="s" s="1">
+        <v>537</v>
+      </c>
+      <c r="C146" t="s" s="1">
+        <v>538</v>
+      </c>
+      <c r="D146" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="E146" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="F146" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="G146" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="H146" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A147" t="n" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147" t="s" s="1">
+        <v>542</v>
+      </c>
+      <c r="C147" t="s" s="1">
+        <v>543</v>
+      </c>
+      <c r="D147" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="E147" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="F147" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="G147" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="H147" t="n" s="3">
+        <v>9600</v>
+      </c>
+      <c r="I147" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n" s="3">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A148" t="n" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148" t="s" s="1">
+        <v>542</v>
+      </c>
+      <c r="C148" t="s" s="1">
+        <v>543</v>
+      </c>
+      <c r="D148" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="E148" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="F148" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="G148" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="H148" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A149" t="n" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149" t="s" s="1">
+        <v>547</v>
+      </c>
+      <c r="C149" t="s" s="1">
+        <v>548</v>
+      </c>
+      <c r="D149" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="E149" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="F149" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="G149" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="H149" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A150" t="n" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150" t="s" s="1">
+        <v>547</v>
+      </c>
+      <c r="C150" t="s" s="1">
+        <v>548</v>
+      </c>
+      <c r="D150" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="E150" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="F150" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="G150" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="H150" t="n" s="3">
+        <v>9600</v>
+      </c>
+      <c r="I150" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n" s="3">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A151" t="n" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151" t="s" s="1">
+        <v>552</v>
+      </c>
+      <c r="C151" t="s" s="1">
+        <v>553</v>
+      </c>
+      <c r="D151" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="E151" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="F151" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="G151" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="H151" t="n" s="3">
+        <v>14000</v>
+      </c>
+      <c r="I151" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A152" t="n" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152" t="s" s="1">
+        <v>557</v>
+      </c>
+      <c r="C152" t="s" s="1">
+        <v>558</v>
+      </c>
+      <c r="D152" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="E152" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="F152" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="G152" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="H152" t="n" s="3">
+        <v>14000</v>
+      </c>
+      <c r="I152" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A153" t="n" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153" t="s" s="1">
+        <v>562</v>
+      </c>
+      <c r="C153" t="s" s="1">
+        <v>563</v>
+      </c>
+      <c r="D153" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="E153" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="F153" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="G153" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="H153" t="n" s="3">
+        <v>14000</v>
+      </c>
+      <c r="I153" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n" s="3">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A154" t="n" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" t="s" s="1">
         <v>567</v>
       </c>
-      <c r="C145" t="s" s="1">
+      <c r="C154" t="s" s="1">
         <v>568</v>
       </c>
-      <c r="D145" t="s" s="2">
+      <c r="D154" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="E145" t="s" s="2">
+      <c r="E154" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="F154" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="G154" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="H154" t="n" s="3">
+        <v>4426.67</v>
+      </c>
+      <c r="I154" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n" s="3">
+        <v>4426.67</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A155" t="n" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155" t="s" s="1">
         <v>572</v>
       </c>
-      <c r="F145" t="s" s="2">
+      <c r="C155" t="s" s="1">
+        <v>573</v>
+      </c>
+      <c r="D155" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="E155" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="F155" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="G155" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="H155" t="n" s="3">
+        <v>4586.67</v>
+      </c>
+      <c r="I155" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n" s="3">
+        <v>4586.67</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A156" t="n" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156" t="s" s="1">
+        <v>577</v>
+      </c>
+      <c r="C156" t="s" s="1">
+        <v>578</v>
+      </c>
+      <c r="D156" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="G145" t="s" s="1">
-        <v>125</v>
-      </c>
-      <c r="H145" t="n" s="3">
+      <c r="E156" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="F156" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="G156" t="s" s="1">
+        <v>125</v>
+      </c>
+      <c r="H156" t="n" s="3">
         <v>4533.33</v>
       </c>
-      <c r="I145" t="n" s="3">
-        <v>0</v>
-      </c>
-      <c r="J145" t="n" s="3">
-        <v>0</v>
-      </c>
-      <c r="K145" t="n" s="3">
+      <c r="I156" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n" s="3">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n" s="3">
         <v>4533.33</v>
       </c>
     </row>
